--- a/artfynd/A 30910-2025 artfynd.xlsx
+++ b/artfynd/A 30910-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +795,297 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126412308</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stora Fräkenviken, Stora Fräkenviken, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>559904</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6510346</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126411973</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stora Fräkenviken, Stora Fräkenviken, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>559822</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6510197</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126412373</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora Fräkenviken, Stora Fräkenviken, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559862</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6510374</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30910-2025 artfynd.xlsx
+++ b/artfynd/A 30910-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,6 +1086,244 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126435733</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105387</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ämtetorp VNV 510 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>559904</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6510345</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126435603</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105387</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ämtetorp VNV 545 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>559838</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6510248</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30910-2025 artfynd.xlsx
+++ b/artfynd/A 30910-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>126412308</v>
       </c>
       <c r="B3" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>126412373</v>
       </c>
       <c r="B5" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>126435733</v>
       </c>
       <c r="B6" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>126435603</v>
       </c>
       <c r="B7" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
